--- a/students/ترابیsum2.2OK.xlsx
+++ b/students/ترابیsum2.2OK.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB352D9C-9C5B-4A7B-8AC5-E459D3B30A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -117,12 +118,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -135,7 +136,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -191,17 +192,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -474,21 +489,21 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:TA14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:TA18"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="41.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.296875" customWidth="1"/>
+    <col min="7" max="7" width="41.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:521" x14ac:dyDescent="0.25">
@@ -578,520 +593,520 @@
       <c r="G4" s="1">
         <v>9012314651</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
-      <c r="AD4" s="4"/>
-      <c r="AE4" s="4"/>
-      <c r="AF4" s="4"/>
-      <c r="AG4" s="4"/>
-      <c r="AH4" s="4"/>
-      <c r="AI4" s="4"/>
-      <c r="AJ4" s="4"/>
-      <c r="AK4" s="4"/>
-      <c r="AL4" s="4"/>
-      <c r="AM4" s="4"/>
-      <c r="AN4" s="4"/>
-      <c r="AO4" s="4"/>
-      <c r="AP4" s="4"/>
-      <c r="AQ4" s="4"/>
-      <c r="AR4" s="4"/>
-      <c r="AS4" s="4"/>
-      <c r="AT4" s="4"/>
-      <c r="AU4" s="4"/>
-      <c r="AV4" s="4"/>
-      <c r="AW4" s="4"/>
-      <c r="AX4" s="4"/>
-      <c r="AY4" s="4"/>
-      <c r="AZ4" s="4"/>
-      <c r="BA4" s="4"/>
-      <c r="BB4" s="4"/>
-      <c r="BC4" s="4"/>
-      <c r="BD4" s="4"/>
-      <c r="BE4" s="4"/>
-      <c r="BF4" s="4"/>
-      <c r="BG4" s="4"/>
-      <c r="BH4" s="4"/>
-      <c r="BI4" s="4"/>
-      <c r="BJ4" s="4"/>
-      <c r="BK4" s="4"/>
-      <c r="BL4" s="4"/>
-      <c r="BM4" s="4"/>
-      <c r="BN4" s="4"/>
-      <c r="BO4" s="4"/>
-      <c r="BP4" s="4"/>
-      <c r="BQ4" s="4"/>
-      <c r="BR4" s="4"/>
-      <c r="BS4" s="4"/>
-      <c r="BT4" s="4"/>
-      <c r="BU4" s="4"/>
-      <c r="BV4" s="4"/>
-      <c r="BW4" s="4"/>
-      <c r="BX4" s="4"/>
-      <c r="BY4" s="4"/>
-      <c r="BZ4" s="4"/>
-      <c r="CA4" s="4"/>
-      <c r="CB4" s="4"/>
-      <c r="CC4" s="4"/>
-      <c r="CD4" s="4"/>
-      <c r="CE4" s="4"/>
-      <c r="CF4" s="4"/>
-      <c r="CG4" s="4"/>
-      <c r="CH4" s="4"/>
-      <c r="CI4" s="4"/>
-      <c r="CJ4" s="4"/>
-      <c r="CK4" s="4"/>
-      <c r="CL4" s="4"/>
-      <c r="CM4" s="4"/>
-      <c r="CN4" s="4"/>
-      <c r="CO4" s="4"/>
-      <c r="CP4" s="4"/>
-      <c r="CQ4" s="4"/>
-      <c r="CR4" s="4"/>
-      <c r="CS4" s="4"/>
-      <c r="CT4" s="4"/>
-      <c r="CU4" s="4"/>
-      <c r="CV4" s="4"/>
-      <c r="CW4" s="4"/>
-      <c r="CX4" s="4"/>
-      <c r="CY4" s="4"/>
-      <c r="CZ4" s="4"/>
-      <c r="DA4" s="4"/>
-      <c r="DB4" s="4"/>
-      <c r="DC4" s="4"/>
-      <c r="DD4" s="4"/>
-      <c r="DE4" s="4"/>
-      <c r="DF4" s="4"/>
-      <c r="DG4" s="4"/>
-      <c r="DH4" s="4"/>
-      <c r="DI4" s="4"/>
-      <c r="DJ4" s="4"/>
-      <c r="DK4" s="4"/>
-      <c r="DL4" s="4"/>
-      <c r="DM4" s="4"/>
-      <c r="DN4" s="4"/>
-      <c r="DO4" s="4"/>
-      <c r="DP4" s="4"/>
-      <c r="DQ4" s="4"/>
-      <c r="DR4" s="4"/>
-      <c r="DS4" s="4"/>
-      <c r="DT4" s="4"/>
-      <c r="DU4" s="4"/>
-      <c r="DV4" s="4"/>
-      <c r="DW4" s="4"/>
-      <c r="DX4" s="4"/>
-      <c r="DY4" s="4"/>
-      <c r="DZ4" s="4"/>
-      <c r="EA4" s="4"/>
-      <c r="EB4" s="4"/>
-      <c r="EC4" s="4"/>
-      <c r="ED4" s="4"/>
-      <c r="EE4" s="4"/>
-      <c r="EF4" s="4"/>
-      <c r="EG4" s="4"/>
-      <c r="EH4" s="4"/>
-      <c r="EI4" s="4"/>
-      <c r="EJ4" s="4"/>
-      <c r="EK4" s="4"/>
-      <c r="EL4" s="4"/>
-      <c r="EM4" s="4"/>
-      <c r="EN4" s="4"/>
-      <c r="EO4" s="4"/>
-      <c r="EP4" s="4"/>
-      <c r="EQ4" s="4"/>
-      <c r="ER4" s="4"/>
-      <c r="ES4" s="4"/>
-      <c r="ET4" s="4"/>
-      <c r="EU4" s="4"/>
-      <c r="EV4" s="4"/>
-      <c r="EW4" s="4"/>
-      <c r="EX4" s="4"/>
-      <c r="EY4" s="4"/>
-      <c r="EZ4" s="4"/>
-      <c r="FA4" s="4"/>
-      <c r="FB4" s="4"/>
-      <c r="FC4" s="4"/>
-      <c r="FD4" s="4"/>
-      <c r="FE4" s="4"/>
-      <c r="FF4" s="4"/>
-      <c r="FG4" s="4"/>
-      <c r="FH4" s="4"/>
-      <c r="FI4" s="4"/>
-      <c r="FJ4" s="4"/>
-      <c r="FK4" s="4"/>
-      <c r="FL4" s="4"/>
-      <c r="FM4" s="4"/>
-      <c r="FN4" s="4"/>
-      <c r="FO4" s="4"/>
-      <c r="FP4" s="4"/>
-      <c r="FQ4" s="4"/>
-      <c r="FR4" s="4"/>
-      <c r="FS4" s="4"/>
-      <c r="FT4" s="4"/>
-      <c r="FU4" s="4"/>
-      <c r="FV4" s="4"/>
-      <c r="FW4" s="4"/>
-      <c r="FX4" s="4"/>
-      <c r="FY4" s="4"/>
-      <c r="FZ4" s="4"/>
-      <c r="GA4" s="4"/>
-      <c r="GB4" s="4"/>
-      <c r="GC4" s="4"/>
-      <c r="GD4" s="4"/>
-      <c r="GE4" s="4"/>
-      <c r="GF4" s="4"/>
-      <c r="GG4" s="4"/>
-      <c r="GH4" s="4"/>
-      <c r="GI4" s="4"/>
-      <c r="GJ4" s="4"/>
-      <c r="GK4" s="4"/>
-      <c r="GL4" s="4"/>
-      <c r="GM4" s="4"/>
-      <c r="GN4" s="4"/>
-      <c r="GO4" s="4"/>
-      <c r="GP4" s="4"/>
-      <c r="GQ4" s="4"/>
-      <c r="GR4" s="4"/>
-      <c r="GS4" s="4"/>
-      <c r="GT4" s="4"/>
-      <c r="GU4" s="4"/>
-      <c r="GV4" s="4"/>
-      <c r="GW4" s="4"/>
-      <c r="GX4" s="4"/>
-      <c r="GY4" s="4"/>
-      <c r="GZ4" s="4"/>
-      <c r="HA4" s="4"/>
-      <c r="HB4" s="4"/>
-      <c r="HC4" s="4"/>
-      <c r="HD4" s="4"/>
-      <c r="HE4" s="4"/>
-      <c r="HF4" s="4"/>
-      <c r="HG4" s="4"/>
-      <c r="HH4" s="4"/>
-      <c r="HI4" s="4"/>
-      <c r="HJ4" s="4"/>
-      <c r="HK4" s="4"/>
-      <c r="HL4" s="4"/>
-      <c r="HM4" s="4"/>
-      <c r="HN4" s="4"/>
-      <c r="HO4" s="4"/>
-      <c r="HP4" s="4"/>
-      <c r="HQ4" s="4"/>
-      <c r="HR4" s="4"/>
-      <c r="HS4" s="4"/>
-      <c r="HT4" s="4"/>
-      <c r="HU4" s="4"/>
-      <c r="HV4" s="4"/>
-      <c r="HW4" s="4"/>
-      <c r="HX4" s="4"/>
-      <c r="HY4" s="4"/>
-      <c r="HZ4" s="4"/>
-      <c r="IA4" s="4"/>
-      <c r="IB4" s="4"/>
-      <c r="IC4" s="4"/>
-      <c r="ID4" s="4"/>
-      <c r="IE4" s="4"/>
-      <c r="IF4" s="4"/>
-      <c r="IG4" s="4"/>
-      <c r="IH4" s="4"/>
-      <c r="II4" s="4"/>
-      <c r="IJ4" s="4"/>
-      <c r="IK4" s="4"/>
-      <c r="IL4" s="4"/>
-      <c r="IM4" s="4"/>
-      <c r="IN4" s="4"/>
-      <c r="IO4" s="4"/>
-      <c r="IP4" s="4"/>
-      <c r="IQ4" s="4"/>
-      <c r="IR4" s="4"/>
-      <c r="IS4" s="4"/>
-      <c r="IT4" s="4"/>
-      <c r="IU4" s="4"/>
-      <c r="IV4" s="4"/>
-      <c r="IW4" s="4"/>
-      <c r="IX4" s="4"/>
-      <c r="IY4" s="4"/>
-      <c r="IZ4" s="4"/>
-      <c r="JA4" s="4"/>
-      <c r="JB4" s="4"/>
-      <c r="JC4" s="4"/>
-      <c r="JD4" s="4"/>
-      <c r="JE4" s="4"/>
-      <c r="JF4" s="4"/>
-      <c r="JG4" s="4"/>
-      <c r="JH4" s="4"/>
-      <c r="JI4" s="4"/>
-      <c r="JJ4" s="4"/>
-      <c r="JK4" s="4"/>
-      <c r="JL4" s="4"/>
-      <c r="JM4" s="4"/>
-      <c r="JN4" s="4"/>
-      <c r="JO4" s="4"/>
-      <c r="JP4" s="4"/>
-      <c r="JQ4" s="4"/>
-      <c r="JR4" s="4"/>
-      <c r="JS4" s="4"/>
-      <c r="JT4" s="4"/>
-      <c r="JU4" s="4"/>
-      <c r="JV4" s="4"/>
-      <c r="JW4" s="4"/>
-      <c r="JX4" s="4"/>
-      <c r="JY4" s="4"/>
-      <c r="JZ4" s="4"/>
-      <c r="KA4" s="4"/>
-      <c r="KB4" s="4"/>
-      <c r="KC4" s="4"/>
-      <c r="KD4" s="4"/>
-      <c r="KE4" s="4"/>
-      <c r="KF4" s="4"/>
-      <c r="KG4" s="4"/>
-      <c r="KH4" s="4"/>
-      <c r="KI4" s="4"/>
-      <c r="KJ4" s="4"/>
-      <c r="KK4" s="4"/>
-      <c r="KL4" s="4"/>
-      <c r="KM4" s="4"/>
-      <c r="KN4" s="4"/>
-      <c r="KO4" s="4"/>
-      <c r="KP4" s="4"/>
-      <c r="KQ4" s="4"/>
-      <c r="KR4" s="4"/>
-      <c r="KS4" s="4"/>
-      <c r="KT4" s="4"/>
-      <c r="KU4" s="4"/>
-      <c r="KV4" s="4"/>
-      <c r="KW4" s="4"/>
-      <c r="KX4" s="4"/>
-      <c r="KY4" s="4"/>
-      <c r="KZ4" s="4"/>
-      <c r="LA4" s="4"/>
-      <c r="LB4" s="4"/>
-      <c r="LC4" s="4"/>
-      <c r="LD4" s="4"/>
-      <c r="LE4" s="4"/>
-      <c r="LF4" s="4"/>
-      <c r="LG4" s="4"/>
-      <c r="LH4" s="4"/>
-      <c r="LI4" s="4"/>
-      <c r="LJ4" s="4"/>
-      <c r="LK4" s="4"/>
-      <c r="LL4" s="4"/>
-      <c r="LM4" s="4"/>
-      <c r="LN4" s="4"/>
-      <c r="LO4" s="4"/>
-      <c r="LP4" s="4"/>
-      <c r="LQ4" s="4"/>
-      <c r="LR4" s="4"/>
-      <c r="LS4" s="4"/>
-      <c r="LT4" s="4"/>
-      <c r="LU4" s="4"/>
-      <c r="LV4" s="4"/>
-      <c r="LW4" s="4"/>
-      <c r="LX4" s="4"/>
-      <c r="LY4" s="4"/>
-      <c r="LZ4" s="4"/>
-      <c r="MA4" s="4"/>
-      <c r="MB4" s="4"/>
-      <c r="MC4" s="4"/>
-      <c r="MD4" s="4"/>
-      <c r="ME4" s="4"/>
-      <c r="MF4" s="4"/>
-      <c r="MG4" s="4"/>
-      <c r="MH4" s="4"/>
-      <c r="MI4" s="4"/>
-      <c r="MJ4" s="4"/>
-      <c r="MK4" s="4"/>
-      <c r="ML4" s="4"/>
-      <c r="MM4" s="4"/>
-      <c r="MN4" s="4"/>
-      <c r="MO4" s="4"/>
-      <c r="MP4" s="4"/>
-      <c r="MQ4" s="4"/>
-      <c r="MR4" s="4"/>
-      <c r="MS4" s="4"/>
-      <c r="MT4" s="4"/>
-      <c r="MU4" s="4"/>
-      <c r="MV4" s="4"/>
-      <c r="MW4" s="4"/>
-      <c r="MX4" s="4"/>
-      <c r="MY4" s="4"/>
-      <c r="MZ4" s="4"/>
-      <c r="NA4" s="4"/>
-      <c r="NB4" s="4"/>
-      <c r="NC4" s="4"/>
-      <c r="ND4" s="4"/>
-      <c r="NE4" s="4"/>
-      <c r="NF4" s="4"/>
-      <c r="NG4" s="4"/>
-      <c r="NH4" s="4"/>
-      <c r="NI4" s="4"/>
-      <c r="NJ4" s="4"/>
-      <c r="NK4" s="4"/>
-      <c r="NL4" s="4"/>
-      <c r="NM4" s="4"/>
-      <c r="NN4" s="4"/>
-      <c r="NO4" s="4"/>
-      <c r="NP4" s="4"/>
-      <c r="NQ4" s="4"/>
-      <c r="NR4" s="4"/>
-      <c r="NS4" s="4"/>
-      <c r="NT4" s="4"/>
-      <c r="NU4" s="4"/>
-      <c r="NV4" s="4"/>
-      <c r="NW4" s="4"/>
-      <c r="NX4" s="4"/>
-      <c r="NY4" s="4"/>
-      <c r="NZ4" s="4"/>
-      <c r="OA4" s="4"/>
-      <c r="OB4" s="4"/>
-      <c r="OC4" s="4"/>
-      <c r="OD4" s="4"/>
-      <c r="OE4" s="4"/>
-      <c r="OF4" s="4"/>
-      <c r="OG4" s="4"/>
-      <c r="OH4" s="4"/>
-      <c r="OI4" s="4"/>
-      <c r="OJ4" s="4"/>
-      <c r="OK4" s="4"/>
-      <c r="OL4" s="4"/>
-      <c r="OM4" s="4"/>
-      <c r="ON4" s="4"/>
-      <c r="OO4" s="4"/>
-      <c r="OP4" s="4"/>
-      <c r="OQ4" s="4"/>
-      <c r="OR4" s="4"/>
-      <c r="OS4" s="4"/>
-      <c r="OT4" s="4"/>
-      <c r="OU4" s="4"/>
-      <c r="OV4" s="4"/>
-      <c r="OW4" s="4"/>
-      <c r="OX4" s="4"/>
-      <c r="OY4" s="4"/>
-      <c r="OZ4" s="4"/>
-      <c r="PA4" s="4"/>
-      <c r="PB4" s="4"/>
-      <c r="PC4" s="4"/>
-      <c r="PD4" s="4"/>
-      <c r="PE4" s="4"/>
-      <c r="PF4" s="4"/>
-      <c r="PG4" s="4"/>
-      <c r="PH4" s="4"/>
-      <c r="PI4" s="4"/>
-      <c r="PJ4" s="4"/>
-      <c r="PK4" s="4"/>
-      <c r="PL4" s="4"/>
-      <c r="PM4" s="4"/>
-      <c r="PN4" s="4"/>
-      <c r="PO4" s="4"/>
-      <c r="PP4" s="4"/>
-      <c r="PQ4" s="4"/>
-      <c r="PR4" s="4"/>
-      <c r="PS4" s="4"/>
-      <c r="PT4" s="4"/>
-      <c r="PU4" s="4"/>
-      <c r="PV4" s="4"/>
-      <c r="PW4" s="4"/>
-      <c r="PX4" s="4"/>
-      <c r="PY4" s="4"/>
-      <c r="PZ4" s="4"/>
-      <c r="QA4" s="4"/>
-      <c r="QB4" s="4"/>
-      <c r="QC4" s="4"/>
-      <c r="QD4" s="4"/>
-      <c r="QE4" s="4"/>
-      <c r="QF4" s="4"/>
-      <c r="QG4" s="4"/>
-      <c r="QH4" s="4"/>
-      <c r="QI4" s="4"/>
-      <c r="QJ4" s="4"/>
-      <c r="QK4" s="4"/>
-      <c r="QL4" s="4"/>
-      <c r="QM4" s="4"/>
-      <c r="QN4" s="4"/>
-      <c r="QO4" s="4"/>
-      <c r="QP4" s="4"/>
-      <c r="QQ4" s="4"/>
-      <c r="QR4" s="4"/>
-      <c r="QS4" s="4"/>
-      <c r="QT4" s="4"/>
-      <c r="QU4" s="4"/>
-      <c r="QV4" s="4"/>
-      <c r="QW4" s="4"/>
-      <c r="QX4" s="4"/>
-      <c r="QY4" s="4"/>
-      <c r="QZ4" s="4"/>
-      <c r="RA4" s="4"/>
-      <c r="RB4" s="4"/>
-      <c r="RC4" s="4"/>
-      <c r="RD4" s="4"/>
-      <c r="RE4" s="4"/>
-      <c r="RF4" s="4"/>
-      <c r="RG4" s="4"/>
-      <c r="RH4" s="4"/>
-      <c r="RI4" s="4"/>
-      <c r="RJ4" s="4"/>
-      <c r="RK4" s="4"/>
-      <c r="RL4" s="4"/>
-      <c r="RM4" s="4"/>
-      <c r="RN4" s="4"/>
-      <c r="RO4" s="4"/>
-      <c r="RP4" s="4"/>
-      <c r="RQ4" s="4"/>
-      <c r="RR4" s="4"/>
-      <c r="RS4" s="4"/>
-      <c r="RT4" s="4"/>
-      <c r="RU4" s="4"/>
-      <c r="RV4" s="4"/>
-      <c r="RW4" s="4"/>
-      <c r="RX4" s="4"/>
-      <c r="RY4" s="4"/>
-      <c r="RZ4" s="4"/>
-      <c r="SA4" s="4"/>
-      <c r="SB4" s="4"/>
-      <c r="SC4" s="4"/>
-      <c r="SD4" s="4"/>
-      <c r="SE4" s="4"/>
-      <c r="SF4" s="4"/>
-      <c r="SG4" s="4"/>
-      <c r="SH4" s="4"/>
-      <c r="SI4" s="4"/>
-      <c r="SJ4" s="4"/>
-      <c r="SK4" s="4"/>
-      <c r="SL4" s="4"/>
-      <c r="SM4" s="4"/>
-      <c r="SN4" s="4"/>
-      <c r="SO4" s="4"/>
-      <c r="SP4" s="4"/>
-      <c r="SQ4" s="4"/>
-      <c r="SR4" s="4"/>
-      <c r="SS4" s="4"/>
-      <c r="ST4" s="4"/>
-      <c r="SU4" s="4"/>
-      <c r="SV4" s="4"/>
-      <c r="SW4" s="4"/>
-      <c r="SX4" s="4"/>
-      <c r="SY4" s="4"/>
-      <c r="SZ4" s="4"/>
-      <c r="TA4" s="4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4"/>
+      <c r="S4"/>
+      <c r="T4"/>
+      <c r="U4"/>
+      <c r="V4"/>
+      <c r="W4"/>
+      <c r="X4"/>
+      <c r="Y4"/>
+      <c r="Z4"/>
+      <c r="AA4"/>
+      <c r="AB4"/>
+      <c r="AC4"/>
+      <c r="AD4"/>
+      <c r="AE4"/>
+      <c r="AF4"/>
+      <c r="AG4"/>
+      <c r="AH4"/>
+      <c r="AI4"/>
+      <c r="AJ4"/>
+      <c r="AK4"/>
+      <c r="AL4"/>
+      <c r="AM4"/>
+      <c r="AN4"/>
+      <c r="AO4"/>
+      <c r="AP4"/>
+      <c r="AQ4"/>
+      <c r="AR4"/>
+      <c r="AS4"/>
+      <c r="AT4"/>
+      <c r="AU4"/>
+      <c r="AV4"/>
+      <c r="AW4"/>
+      <c r="AX4"/>
+      <c r="AY4"/>
+      <c r="AZ4"/>
+      <c r="BA4"/>
+      <c r="BB4"/>
+      <c r="BC4"/>
+      <c r="BD4"/>
+      <c r="BE4"/>
+      <c r="BF4"/>
+      <c r="BG4"/>
+      <c r="BH4"/>
+      <c r="BI4"/>
+      <c r="BJ4"/>
+      <c r="BK4"/>
+      <c r="BL4"/>
+      <c r="BM4"/>
+      <c r="BN4"/>
+      <c r="BO4"/>
+      <c r="BP4"/>
+      <c r="BQ4"/>
+      <c r="BR4"/>
+      <c r="BS4"/>
+      <c r="BT4"/>
+      <c r="BU4"/>
+      <c r="BV4"/>
+      <c r="BW4"/>
+      <c r="BX4"/>
+      <c r="BY4"/>
+      <c r="BZ4"/>
+      <c r="CA4"/>
+      <c r="CB4"/>
+      <c r="CC4"/>
+      <c r="CD4"/>
+      <c r="CE4"/>
+      <c r="CF4"/>
+      <c r="CG4"/>
+      <c r="CH4"/>
+      <c r="CI4"/>
+      <c r="CJ4"/>
+      <c r="CK4"/>
+      <c r="CL4"/>
+      <c r="CM4"/>
+      <c r="CN4"/>
+      <c r="CO4"/>
+      <c r="CP4"/>
+      <c r="CQ4"/>
+      <c r="CR4"/>
+      <c r="CS4"/>
+      <c r="CT4"/>
+      <c r="CU4"/>
+      <c r="CV4"/>
+      <c r="CW4"/>
+      <c r="CX4"/>
+      <c r="CY4"/>
+      <c r="CZ4"/>
+      <c r="DA4"/>
+      <c r="DB4"/>
+      <c r="DC4"/>
+      <c r="DD4"/>
+      <c r="DE4"/>
+      <c r="DF4"/>
+      <c r="DG4"/>
+      <c r="DH4"/>
+      <c r="DI4"/>
+      <c r="DJ4"/>
+      <c r="DK4"/>
+      <c r="DL4"/>
+      <c r="DM4"/>
+      <c r="DN4"/>
+      <c r="DO4"/>
+      <c r="DP4"/>
+      <c r="DQ4"/>
+      <c r="DR4"/>
+      <c r="DS4"/>
+      <c r="DT4"/>
+      <c r="DU4"/>
+      <c r="DV4"/>
+      <c r="DW4"/>
+      <c r="DX4"/>
+      <c r="DY4"/>
+      <c r="DZ4"/>
+      <c r="EA4"/>
+      <c r="EB4"/>
+      <c r="EC4"/>
+      <c r="ED4"/>
+      <c r="EE4"/>
+      <c r="EF4"/>
+      <c r="EG4"/>
+      <c r="EH4"/>
+      <c r="EI4"/>
+      <c r="EJ4"/>
+      <c r="EK4"/>
+      <c r="EL4"/>
+      <c r="EM4"/>
+      <c r="EN4"/>
+      <c r="EO4"/>
+      <c r="EP4"/>
+      <c r="EQ4"/>
+      <c r="ER4"/>
+      <c r="ES4"/>
+      <c r="ET4"/>
+      <c r="EU4"/>
+      <c r="EV4"/>
+      <c r="EW4"/>
+      <c r="EX4"/>
+      <c r="EY4"/>
+      <c r="EZ4"/>
+      <c r="FA4"/>
+      <c r="FB4"/>
+      <c r="FC4"/>
+      <c r="FD4"/>
+      <c r="FE4"/>
+      <c r="FF4"/>
+      <c r="FG4"/>
+      <c r="FH4"/>
+      <c r="FI4"/>
+      <c r="FJ4"/>
+      <c r="FK4"/>
+      <c r="FL4"/>
+      <c r="FM4"/>
+      <c r="FN4"/>
+      <c r="FO4"/>
+      <c r="FP4"/>
+      <c r="FQ4"/>
+      <c r="FR4"/>
+      <c r="FS4"/>
+      <c r="FT4"/>
+      <c r="FU4"/>
+      <c r="FV4"/>
+      <c r="FW4"/>
+      <c r="FX4"/>
+      <c r="FY4"/>
+      <c r="FZ4"/>
+      <c r="GA4"/>
+      <c r="GB4"/>
+      <c r="GC4"/>
+      <c r="GD4"/>
+      <c r="GE4"/>
+      <c r="GF4"/>
+      <c r="GG4"/>
+      <c r="GH4"/>
+      <c r="GI4"/>
+      <c r="GJ4"/>
+      <c r="GK4"/>
+      <c r="GL4"/>
+      <c r="GM4"/>
+      <c r="GN4"/>
+      <c r="GO4"/>
+      <c r="GP4"/>
+      <c r="GQ4"/>
+      <c r="GR4"/>
+      <c r="GS4"/>
+      <c r="GT4"/>
+      <c r="GU4"/>
+      <c r="GV4"/>
+      <c r="GW4"/>
+      <c r="GX4"/>
+      <c r="GY4"/>
+      <c r="GZ4"/>
+      <c r="HA4"/>
+      <c r="HB4"/>
+      <c r="HC4"/>
+      <c r="HD4"/>
+      <c r="HE4"/>
+      <c r="HF4"/>
+      <c r="HG4"/>
+      <c r="HH4"/>
+      <c r="HI4"/>
+      <c r="HJ4"/>
+      <c r="HK4"/>
+      <c r="HL4"/>
+      <c r="HM4"/>
+      <c r="HN4"/>
+      <c r="HO4"/>
+      <c r="HP4"/>
+      <c r="HQ4"/>
+      <c r="HR4"/>
+      <c r="HS4"/>
+      <c r="HT4"/>
+      <c r="HU4"/>
+      <c r="HV4"/>
+      <c r="HW4"/>
+      <c r="HX4"/>
+      <c r="HY4"/>
+      <c r="HZ4"/>
+      <c r="IA4"/>
+      <c r="IB4"/>
+      <c r="IC4"/>
+      <c r="ID4"/>
+      <c r="IE4"/>
+      <c r="IF4"/>
+      <c r="IG4"/>
+      <c r="IH4"/>
+      <c r="II4"/>
+      <c r="IJ4"/>
+      <c r="IK4"/>
+      <c r="IL4"/>
+      <c r="IM4"/>
+      <c r="IN4"/>
+      <c r="IO4"/>
+      <c r="IP4"/>
+      <c r="IQ4"/>
+      <c r="IR4"/>
+      <c r="IS4"/>
+      <c r="IT4"/>
+      <c r="IU4"/>
+      <c r="IV4"/>
+      <c r="IW4"/>
+      <c r="IX4"/>
+      <c r="IY4"/>
+      <c r="IZ4"/>
+      <c r="JA4"/>
+      <c r="JB4"/>
+      <c r="JC4"/>
+      <c r="JD4"/>
+      <c r="JE4"/>
+      <c r="JF4"/>
+      <c r="JG4"/>
+      <c r="JH4"/>
+      <c r="JI4"/>
+      <c r="JJ4"/>
+      <c r="JK4"/>
+      <c r="JL4"/>
+      <c r="JM4"/>
+      <c r="JN4"/>
+      <c r="JO4"/>
+      <c r="JP4"/>
+      <c r="JQ4"/>
+      <c r="JR4"/>
+      <c r="JS4"/>
+      <c r="JT4"/>
+      <c r="JU4"/>
+      <c r="JV4"/>
+      <c r="JW4"/>
+      <c r="JX4"/>
+      <c r="JY4"/>
+      <c r="JZ4"/>
+      <c r="KA4"/>
+      <c r="KB4"/>
+      <c r="KC4"/>
+      <c r="KD4"/>
+      <c r="KE4"/>
+      <c r="KF4"/>
+      <c r="KG4"/>
+      <c r="KH4"/>
+      <c r="KI4"/>
+      <c r="KJ4"/>
+      <c r="KK4"/>
+      <c r="KL4"/>
+      <c r="KM4"/>
+      <c r="KN4"/>
+      <c r="KO4"/>
+      <c r="KP4"/>
+      <c r="KQ4"/>
+      <c r="KR4"/>
+      <c r="KS4"/>
+      <c r="KT4"/>
+      <c r="KU4"/>
+      <c r="KV4"/>
+      <c r="KW4"/>
+      <c r="KX4"/>
+      <c r="KY4"/>
+      <c r="KZ4"/>
+      <c r="LA4"/>
+      <c r="LB4"/>
+      <c r="LC4"/>
+      <c r="LD4"/>
+      <c r="LE4"/>
+      <c r="LF4"/>
+      <c r="LG4"/>
+      <c r="LH4"/>
+      <c r="LI4"/>
+      <c r="LJ4"/>
+      <c r="LK4"/>
+      <c r="LL4"/>
+      <c r="LM4"/>
+      <c r="LN4"/>
+      <c r="LO4"/>
+      <c r="LP4"/>
+      <c r="LQ4"/>
+      <c r="LR4"/>
+      <c r="LS4"/>
+      <c r="LT4"/>
+      <c r="LU4"/>
+      <c r="LV4"/>
+      <c r="LW4"/>
+      <c r="LX4"/>
+      <c r="LY4"/>
+      <c r="LZ4"/>
+      <c r="MA4"/>
+      <c r="MB4"/>
+      <c r="MC4"/>
+      <c r="MD4"/>
+      <c r="ME4"/>
+      <c r="MF4"/>
+      <c r="MG4"/>
+      <c r="MH4"/>
+      <c r="MI4"/>
+      <c r="MJ4"/>
+      <c r="MK4"/>
+      <c r="ML4"/>
+      <c r="MM4"/>
+      <c r="MN4"/>
+      <c r="MO4"/>
+      <c r="MP4"/>
+      <c r="MQ4"/>
+      <c r="MR4"/>
+      <c r="MS4"/>
+      <c r="MT4"/>
+      <c r="MU4"/>
+      <c r="MV4"/>
+      <c r="MW4"/>
+      <c r="MX4"/>
+      <c r="MY4"/>
+      <c r="MZ4"/>
+      <c r="NA4"/>
+      <c r="NB4"/>
+      <c r="NC4"/>
+      <c r="ND4"/>
+      <c r="NE4"/>
+      <c r="NF4"/>
+      <c r="NG4"/>
+      <c r="NH4"/>
+      <c r="NI4"/>
+      <c r="NJ4"/>
+      <c r="NK4"/>
+      <c r="NL4"/>
+      <c r="NM4"/>
+      <c r="NN4"/>
+      <c r="NO4"/>
+      <c r="NP4"/>
+      <c r="NQ4"/>
+      <c r="NR4"/>
+      <c r="NS4"/>
+      <c r="NT4"/>
+      <c r="NU4"/>
+      <c r="NV4"/>
+      <c r="NW4"/>
+      <c r="NX4"/>
+      <c r="NY4"/>
+      <c r="NZ4"/>
+      <c r="OA4"/>
+      <c r="OB4"/>
+      <c r="OC4"/>
+      <c r="OD4"/>
+      <c r="OE4"/>
+      <c r="OF4"/>
+      <c r="OG4"/>
+      <c r="OH4"/>
+      <c r="OI4"/>
+      <c r="OJ4"/>
+      <c r="OK4"/>
+      <c r="OL4"/>
+      <c r="OM4"/>
+      <c r="ON4"/>
+      <c r="OO4"/>
+      <c r="OP4"/>
+      <c r="OQ4"/>
+      <c r="OR4"/>
+      <c r="OS4"/>
+      <c r="OT4"/>
+      <c r="OU4"/>
+      <c r="OV4"/>
+      <c r="OW4"/>
+      <c r="OX4"/>
+      <c r="OY4"/>
+      <c r="OZ4"/>
+      <c r="PA4"/>
+      <c r="PB4"/>
+      <c r="PC4"/>
+      <c r="PD4"/>
+      <c r="PE4"/>
+      <c r="PF4"/>
+      <c r="PG4"/>
+      <c r="PH4"/>
+      <c r="PI4"/>
+      <c r="PJ4"/>
+      <c r="PK4"/>
+      <c r="PL4"/>
+      <c r="PM4"/>
+      <c r="PN4"/>
+      <c r="PO4"/>
+      <c r="PP4"/>
+      <c r="PQ4"/>
+      <c r="PR4"/>
+      <c r="PS4"/>
+      <c r="PT4"/>
+      <c r="PU4"/>
+      <c r="PV4"/>
+      <c r="PW4"/>
+      <c r="PX4"/>
+      <c r="PY4"/>
+      <c r="PZ4"/>
+      <c r="QA4"/>
+      <c r="QB4"/>
+      <c r="QC4"/>
+      <c r="QD4"/>
+      <c r="QE4"/>
+      <c r="QF4"/>
+      <c r="QG4"/>
+      <c r="QH4"/>
+      <c r="QI4"/>
+      <c r="QJ4"/>
+      <c r="QK4"/>
+      <c r="QL4"/>
+      <c r="QM4"/>
+      <c r="QN4"/>
+      <c r="QO4"/>
+      <c r="QP4"/>
+      <c r="QQ4"/>
+      <c r="QR4"/>
+      <c r="QS4"/>
+      <c r="QT4"/>
+      <c r="QU4"/>
+      <c r="QV4"/>
+      <c r="QW4"/>
+      <c r="QX4"/>
+      <c r="QY4"/>
+      <c r="QZ4"/>
+      <c r="RA4"/>
+      <c r="RB4"/>
+      <c r="RC4"/>
+      <c r="RD4"/>
+      <c r="RE4"/>
+      <c r="RF4"/>
+      <c r="RG4"/>
+      <c r="RH4"/>
+      <c r="RI4"/>
+      <c r="RJ4"/>
+      <c r="RK4"/>
+      <c r="RL4"/>
+      <c r="RM4"/>
+      <c r="RN4"/>
+      <c r="RO4"/>
+      <c r="RP4"/>
+      <c r="RQ4"/>
+      <c r="RR4"/>
+      <c r="RS4"/>
+      <c r="RT4"/>
+      <c r="RU4"/>
+      <c r="RV4"/>
+      <c r="RW4"/>
+      <c r="RX4"/>
+      <c r="RY4"/>
+      <c r="RZ4"/>
+      <c r="SA4"/>
+      <c r="SB4"/>
+      <c r="SC4"/>
+      <c r="SD4"/>
+      <c r="SE4"/>
+      <c r="SF4"/>
+      <c r="SG4"/>
+      <c r="SH4"/>
+      <c r="SI4"/>
+      <c r="SJ4"/>
+      <c r="SK4"/>
+      <c r="SL4"/>
+      <c r="SM4"/>
+      <c r="SN4"/>
+      <c r="SO4"/>
+      <c r="SP4"/>
+      <c r="SQ4"/>
+      <c r="SR4"/>
+      <c r="SS4"/>
+      <c r="ST4"/>
+      <c r="SU4"/>
+      <c r="SV4"/>
+      <c r="SW4"/>
+      <c r="SX4"/>
+      <c r="SY4"/>
+      <c r="SZ4"/>
+      <c r="TA4"/>
     </row>
     <row r="5" spans="1:521" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1163,13 +1178,13 @@
       <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>9454883104</v>
       </c>
       <c r="F8" s="1">
@@ -1243,43 +1258,79 @@
       </c>
     </row>
     <row r="12" spans="1:521" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="A12" s="5">
         <v>10555</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="5">
         <v>90374886386</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="5">
         <v>9191412881</v>
       </c>
-      <c r="G12" s="1"/>
+      <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:521" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
     </row>
     <row r="14" spans="1:521" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="1:521" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="1:521" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
